--- a/Connectivity_Application_Data_TEST_ALL_SHEETS32.xlsx
+++ b/Connectivity_Application_Data_TEST_ALL_SHEETS32.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\CTU-automated-pdf-extraction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1E31CE-2C1A-474E-BE21-EC29FC9A1F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D4A522-90FF-4A55-9FF9-5660621A6E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Sources" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8948" uniqueCount="1527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8815" uniqueCount="1527">
   <si>
     <t>SN</t>
   </si>
@@ -52095,7 +52095,7 @@
       </c>
       <c r="N4" s="15">
         <f ca="1">DATE(YEAR(TODAY()), MONTH(TODAY()+M4), DAY(TODAY()))</f>
-        <v>46028</v>
+        <v>46066</v>
       </c>
       <c r="O4" s="14"/>
       <c r="P4" s="14"/>
@@ -52136,14 +52136,14 @@
       <c r="K5" s="14"/>
       <c r="L5" s="15">
         <f ca="1">TODAY()</f>
-        <v>46028</v>
+        <v>46035</v>
       </c>
       <c r="M5" s="14">
         <v>21</v>
       </c>
       <c r="N5" s="15">
         <f ca="1">DATE(YEAR(L5),MONTH(L5)+M5,DAY(L5))</f>
-        <v>46666</v>
+        <v>46673</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="14"/>
